--- a/artfynd/A 38802-2026 artfynd.xlsx
+++ b/artfynd/A 38802-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137058649</v>
       </c>
       <c r="B2" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137058514</v>
       </c>
       <c r="B3" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>137058931</v>
       </c>
       <c r="B4" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>137059148</v>
       </c>
       <c r="B5" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>137059591</v>
       </c>
       <c r="B6" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>137058825</v>
       </c>
       <c r="B7" t="n">
-        <v>92549</v>
+        <v>92550</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>137059202</v>
       </c>
       <c r="B8" t="n">
-        <v>92549</v>
+        <v>92550</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>137058524</v>
       </c>
       <c r="B9" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>137059438</v>
       </c>
       <c r="B10" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>137059465</v>
       </c>
       <c r="B11" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>137059568</v>
       </c>
       <c r="B12" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>137060099</v>
       </c>
       <c r="B13" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>137060257</v>
       </c>
       <c r="B14" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
         <v>137057925</v>
       </c>
       <c r="B19" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>137057996</v>
       </c>
       <c r="B20" t="n">
-        <v>101473</v>
+        <v>101474</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 38802-2026 artfynd.xlsx
+++ b/artfynd/A 38802-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137058649</v>
       </c>
       <c r="B2" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137058514</v>
       </c>
       <c r="B3" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>137058931</v>
       </c>
       <c r="B4" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>137059148</v>
       </c>
       <c r="B5" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>137059591</v>
       </c>
       <c r="B6" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>137058825</v>
       </c>
       <c r="B7" t="n">
-        <v>92550</v>
+        <v>92556</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>137059202</v>
       </c>
       <c r="B8" t="n">
-        <v>92550</v>
+        <v>92556</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
         <v>137057925</v>
       </c>
       <c r="B19" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>137057996</v>
       </c>
       <c r="B20" t="n">
-        <v>101474</v>
+        <v>101480</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 38802-2026 artfynd.xlsx
+++ b/artfynd/A 38802-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137058649</v>
       </c>
       <c r="B2" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137058514</v>
       </c>
       <c r="B3" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>137058931</v>
       </c>
       <c r="B4" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>137059148</v>
       </c>
       <c r="B5" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>137059591</v>
       </c>
       <c r="B6" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>137058825</v>
       </c>
       <c r="B7" t="n">
-        <v>92556</v>
+        <v>92560</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>137059202</v>
       </c>
       <c r="B8" t="n">
-        <v>92556</v>
+        <v>92560</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>137058524</v>
       </c>
       <c r="B9" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>137059438</v>
       </c>
       <c r="B10" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>137059465</v>
       </c>
       <c r="B11" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>137059568</v>
       </c>
       <c r="B12" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>137060099</v>
       </c>
       <c r="B13" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>137060257</v>
       </c>
       <c r="B14" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
         <v>137057925</v>
       </c>
       <c r="B19" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>137057996</v>
       </c>
       <c r="B20" t="n">
-        <v>101480</v>
+        <v>101484</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 38802-2026 artfynd.xlsx
+++ b/artfynd/A 38802-2026 artfynd.xlsx
@@ -2644,7 +2644,7 @@
         <v>137057925</v>
       </c>
       <c r="B19" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>137057996</v>
       </c>
       <c r="B20" t="n">
-        <v>101484</v>
+        <v>101486</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 38802-2026 artfynd.xlsx
+++ b/artfynd/A 38802-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137058649</v>
       </c>
       <c r="B2" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137058514</v>
       </c>
       <c r="B3" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>137058931</v>
       </c>
       <c r="B4" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>137059148</v>
       </c>
       <c r="B5" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>137059591</v>
       </c>
       <c r="B6" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>137058825</v>
       </c>
       <c r="B7" t="n">
-        <v>92560</v>
+        <v>92562</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>137059202</v>
       </c>
       <c r="B8" t="n">
-        <v>92560</v>
+        <v>92562</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>137058524</v>
       </c>
       <c r="B9" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>137059438</v>
       </c>
       <c r="B10" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>137059465</v>
       </c>
       <c r="B11" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>137059568</v>
       </c>
       <c r="B12" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>137060099</v>
       </c>
       <c r="B13" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>137060257</v>
       </c>
       <c r="B14" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
         <v>137057925</v>
       </c>
       <c r="B19" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>137057996</v>
       </c>
       <c r="B20" t="n">
-        <v>101486</v>
+        <v>101488</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 38802-2026 artfynd.xlsx
+++ b/artfynd/A 38802-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137058649</v>
       </c>
       <c r="B2" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137058514</v>
       </c>
       <c r="B3" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>137058931</v>
       </c>
       <c r="B4" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>137059148</v>
       </c>
       <c r="B5" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>137059591</v>
       </c>
       <c r="B6" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>137058825</v>
       </c>
       <c r="B7" t="n">
-        <v>92562</v>
+        <v>92575</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>137059202</v>
       </c>
       <c r="B8" t="n">
-        <v>92562</v>
+        <v>92575</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>137058524</v>
       </c>
       <c r="B9" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>137059438</v>
       </c>
       <c r="B10" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>137059465</v>
       </c>
       <c r="B11" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>137059568</v>
       </c>
       <c r="B12" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>137060099</v>
       </c>
       <c r="B13" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>137060257</v>
       </c>
       <c r="B14" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>137059066</v>
       </c>
       <c r="B15" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>137059374</v>
       </c>
       <c r="B16" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         <v>137060317</v>
       </c>
       <c r="B17" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2518,7 +2518,7 @@
         <v>137059949</v>
       </c>
       <c r="B18" t="n">
-        <v>58112</v>
+        <v>58125</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
         <v>137057925</v>
       </c>
       <c r="B19" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>137057996</v>
       </c>
       <c r="B20" t="n">
-        <v>101488</v>
+        <v>101501</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 38802-2026 artfynd.xlsx
+++ b/artfynd/A 38802-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137058649</v>
       </c>
       <c r="B2" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137058514</v>
       </c>
       <c r="B3" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>137058931</v>
       </c>
       <c r="B4" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>137059148</v>
       </c>
       <c r="B5" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>137059591</v>
       </c>
       <c r="B6" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>137058825</v>
       </c>
       <c r="B7" t="n">
-        <v>92575</v>
+        <v>92577</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>137059202</v>
       </c>
       <c r="B8" t="n">
-        <v>92575</v>
+        <v>92577</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>137058524</v>
       </c>
       <c r="B9" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>137059438</v>
       </c>
       <c r="B10" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>137059465</v>
       </c>
       <c r="B11" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>137059568</v>
       </c>
       <c r="B12" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>137060099</v>
       </c>
       <c r="B13" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>137060257</v>
       </c>
       <c r="B14" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>137059066</v>
       </c>
       <c r="B15" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>137059374</v>
       </c>
       <c r="B16" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         <v>137060317</v>
       </c>
       <c r="B17" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2518,7 +2518,7 @@
         <v>137059949</v>
       </c>
       <c r="B18" t="n">
-        <v>58125</v>
+        <v>58127</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
         <v>137057925</v>
       </c>
       <c r="B19" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>137057996</v>
       </c>
       <c r="B20" t="n">
-        <v>101501</v>
+        <v>101503</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 38802-2026 artfynd.xlsx
+++ b/artfynd/A 38802-2026 artfynd.xlsx
@@ -713,11 +713,7 @@
           <t>100</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Älggårdsrå, Älggårdsrå, Ång</t>
@@ -2174,11 +2170,7 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Älggårdsrå, Älggårdsrå, Ång</t>
@@ -2296,11 +2288,7 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Älggårdsrå, Älggårdsrå, Ång</t>
@@ -2422,16 +2410,8 @@
           <t>2</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Älggårdsberget, Älggårdsberget, Ång</t>
@@ -2548,16 +2528,8 @@
           <t>2</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Älggårdsrå, Älggårdsrå, Ång</t>

--- a/artfynd/A 38802-2026 artfynd.xlsx
+++ b/artfynd/A 38802-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137058649</v>
       </c>
       <c r="B2" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>137058514</v>
       </c>
       <c r="B3" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>137058931</v>
       </c>
       <c r="B4" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137059148</v>
       </c>
       <c r="B5" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>137059591</v>
       </c>
       <c r="B6" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>137058825</v>
       </c>
       <c r="B7" t="n">
-        <v>92577</v>
+        <v>92580</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>137059202</v>
       </c>
       <c r="B8" t="n">
-        <v>92577</v>
+        <v>92580</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>137057925</v>
       </c>
       <c r="B19" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>137057996</v>
       </c>
       <c r="B20" t="n">
-        <v>101503</v>
+        <v>101506</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 38802-2026 artfynd.xlsx
+++ b/artfynd/A 38802-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137058649</v>
       </c>
       <c r="B2" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>137058514</v>
       </c>
       <c r="B3" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>137058931</v>
       </c>
       <c r="B4" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137059148</v>
       </c>
       <c r="B5" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>137059591</v>
       </c>
       <c r="B6" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>137058825</v>
       </c>
       <c r="B7" t="n">
-        <v>92580</v>
+        <v>92590</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>137059202</v>
       </c>
       <c r="B8" t="n">
-        <v>92580</v>
+        <v>92590</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>137058524</v>
       </c>
       <c r="B9" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>137059438</v>
       </c>
       <c r="B10" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>137059465</v>
       </c>
       <c r="B11" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>137059568</v>
       </c>
       <c r="B12" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>137060099</v>
       </c>
       <c r="B13" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>137060257</v>
       </c>
       <c r="B14" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>137059066</v>
       </c>
       <c r="B15" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>137059374</v>
       </c>
       <c r="B16" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>137060317</v>
       </c>
       <c r="B17" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>137059949</v>
       </c>
       <c r="B18" t="n">
-        <v>58127</v>
+        <v>58137</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>137057925</v>
       </c>
       <c r="B19" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>137057996</v>
       </c>
       <c r="B20" t="n">
-        <v>101506</v>
+        <v>101521</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 38802-2026 artfynd.xlsx
+++ b/artfynd/A 38802-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137058649</v>
       </c>
       <c r="B2" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>137058514</v>
       </c>
       <c r="B3" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>137058931</v>
       </c>
       <c r="B4" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137059148</v>
       </c>
       <c r="B5" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>137059591</v>
       </c>
       <c r="B6" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>137058825</v>
       </c>
       <c r="B7" t="n">
-        <v>92590</v>
+        <v>92591</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>137059202</v>
       </c>
       <c r="B8" t="n">
-        <v>92590</v>
+        <v>92591</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>137057925</v>
       </c>
       <c r="B19" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>137057996</v>
       </c>
       <c r="B20" t="n">
-        <v>101521</v>
+        <v>101522</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 38802-2026 artfynd.xlsx
+++ b/artfynd/A 38802-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137058649</v>
       </c>
       <c r="B2" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>137058514</v>
       </c>
       <c r="B3" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>137058931</v>
       </c>
       <c r="B4" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137059148</v>
       </c>
       <c r="B5" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>137059591</v>
       </c>
       <c r="B6" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>137058825</v>
       </c>
       <c r="B7" t="n">
-        <v>92591</v>
+        <v>92594</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>137059202</v>
       </c>
       <c r="B8" t="n">
-        <v>92591</v>
+        <v>92594</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>137058524</v>
       </c>
       <c r="B9" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>137059438</v>
       </c>
       <c r="B10" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>137059465</v>
       </c>
       <c r="B11" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>137059568</v>
       </c>
       <c r="B12" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>137060099</v>
       </c>
       <c r="B13" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>137060257</v>
       </c>
       <c r="B14" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>137059066</v>
       </c>
       <c r="B15" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>137059374</v>
       </c>
       <c r="B16" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>137060317</v>
       </c>
       <c r="B17" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>137059949</v>
       </c>
       <c r="B18" t="n">
-        <v>58137</v>
+        <v>58138</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>137057925</v>
       </c>
       <c r="B19" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>137057996</v>
       </c>
       <c r="B20" t="n">
-        <v>101522</v>
+        <v>101527</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 38802-2026 artfynd.xlsx
+++ b/artfynd/A 38802-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137058649</v>
       </c>
       <c r="B2" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>137058514</v>
       </c>
       <c r="B3" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>137058931</v>
       </c>
       <c r="B4" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137059148</v>
       </c>
       <c r="B5" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>137059591</v>
       </c>
       <c r="B6" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>137058825</v>
       </c>
       <c r="B7" t="n">
-        <v>92594</v>
+        <v>92596</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>137059202</v>
       </c>
       <c r="B8" t="n">
-        <v>92594</v>
+        <v>92596</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>137057925</v>
       </c>
       <c r="B19" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>137057996</v>
       </c>
       <c r="B20" t="n">
-        <v>101527</v>
+        <v>101530</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 38802-2026 artfynd.xlsx
+++ b/artfynd/A 38802-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137058649</v>
       </c>
       <c r="B2" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>137058514</v>
       </c>
       <c r="B3" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>137058931</v>
       </c>
       <c r="B4" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137059148</v>
       </c>
       <c r="B5" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>137059591</v>
       </c>
       <c r="B6" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>137058825</v>
       </c>
       <c r="B7" t="n">
-        <v>92596</v>
+        <v>92601</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>137059202</v>
       </c>
       <c r="B8" t="n">
-        <v>92596</v>
+        <v>92601</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>137058524</v>
       </c>
       <c r="B9" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>137059438</v>
       </c>
       <c r="B10" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>137059465</v>
       </c>
       <c r="B11" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>137059568</v>
       </c>
       <c r="B12" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>137060099</v>
       </c>
       <c r="B13" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>137060257</v>
       </c>
       <c r="B14" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>137059066</v>
       </c>
       <c r="B15" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>137059374</v>
       </c>
       <c r="B16" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>137060317</v>
       </c>
       <c r="B17" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>137059949</v>
       </c>
       <c r="B18" t="n">
-        <v>58138</v>
+        <v>58139</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>137057925</v>
       </c>
       <c r="B19" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>137057996</v>
       </c>
       <c r="B20" t="n">
-        <v>101530</v>
+        <v>101536</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 38802-2026 artfynd.xlsx
+++ b/artfynd/A 38802-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137058649</v>
       </c>
       <c r="B2" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>137058514</v>
       </c>
       <c r="B3" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>137058931</v>
       </c>
       <c r="B4" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137059148</v>
       </c>
       <c r="B5" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>137059591</v>
       </c>
       <c r="B6" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>137058825</v>
       </c>
       <c r="B7" t="n">
-        <v>92601</v>
+        <v>92613</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>137059202</v>
       </c>
       <c r="B8" t="n">
-        <v>92601</v>
+        <v>92613</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>137058524</v>
       </c>
       <c r="B9" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>137059438</v>
       </c>
       <c r="B10" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>137059465</v>
       </c>
       <c r="B11" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>137059568</v>
       </c>
       <c r="B12" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>137060099</v>
       </c>
       <c r="B13" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>137060257</v>
       </c>
       <c r="B14" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>137057925</v>
       </c>
       <c r="B19" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>137057996</v>
       </c>
       <c r="B20" t="n">
-        <v>101536</v>
+        <v>101548</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 38802-2026 artfynd.xlsx
+++ b/artfynd/A 38802-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137058649</v>
       </c>
       <c r="B2" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>137058514</v>
       </c>
       <c r="B3" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>137058931</v>
       </c>
       <c r="B4" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137059148</v>
       </c>
       <c r="B5" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>137059591</v>
       </c>
       <c r="B6" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>137058825</v>
       </c>
       <c r="B7" t="n">
-        <v>92613</v>
+        <v>92614</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>137059202</v>
       </c>
       <c r="B8" t="n">
-        <v>92613</v>
+        <v>92614</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>137058524</v>
       </c>
       <c r="B9" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>137059438</v>
       </c>
       <c r="B10" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>137059465</v>
       </c>
       <c r="B11" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>137059568</v>
       </c>
       <c r="B12" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>137060099</v>
       </c>
       <c r="B13" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>137060257</v>
       </c>
       <c r="B14" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>137057925</v>
       </c>
       <c r="B19" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>137057996</v>
       </c>
       <c r="B20" t="n">
-        <v>101548</v>
+        <v>101549</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 38802-2026 artfynd.xlsx
+++ b/artfynd/A 38802-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137058649</v>
       </c>
       <c r="B2" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>137058514</v>
       </c>
       <c r="B3" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>137058931</v>
       </c>
       <c r="B4" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137059148</v>
       </c>
       <c r="B5" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>137059591</v>
       </c>
       <c r="B6" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>137058825</v>
       </c>
       <c r="B7" t="n">
-        <v>92614</v>
+        <v>92617</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>137059202</v>
       </c>
       <c r="B8" t="n">
-        <v>92614</v>
+        <v>92617</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>137058524</v>
       </c>
       <c r="B9" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>137059438</v>
       </c>
       <c r="B10" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>137059465</v>
       </c>
       <c r="B11" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>137059568</v>
       </c>
       <c r="B12" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>137060099</v>
       </c>
       <c r="B13" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>137060257</v>
       </c>
       <c r="B14" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>137057925</v>
       </c>
       <c r="B19" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>137057996</v>
       </c>
       <c r="B20" t="n">
-        <v>101549</v>
+        <v>101552</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 38802-2026 artfynd.xlsx
+++ b/artfynd/A 38802-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137058649</v>
       </c>
       <c r="B2" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>137058514</v>
       </c>
       <c r="B3" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>137058931</v>
       </c>
       <c r="B4" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>137059148</v>
       </c>
       <c r="B5" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>137059591</v>
       </c>
       <c r="B6" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>137058825</v>
       </c>
       <c r="B7" t="n">
-        <v>92617</v>
+        <v>92621</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>137059202</v>
       </c>
       <c r="B8" t="n">
-        <v>92617</v>
+        <v>92621</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>137058524</v>
       </c>
       <c r="B9" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>137059438</v>
       </c>
       <c r="B10" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>137059465</v>
       </c>
       <c r="B11" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>137059568</v>
       </c>
       <c r="B12" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>137060099</v>
       </c>
       <c r="B13" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>137060257</v>
       </c>
       <c r="B14" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>137059066</v>
       </c>
       <c r="B15" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>137059374</v>
       </c>
       <c r="B16" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>137060317</v>
       </c>
       <c r="B17" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>137059949</v>
       </c>
       <c r="B18" t="n">
-        <v>58139</v>
+        <v>58142</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>137057925</v>
       </c>
       <c r="B19" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>137057996</v>
       </c>
       <c r="B20" t="n">
-        <v>101552</v>
+        <v>101556</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
